--- a/assets/xlsx/일별투자수익_2026-08-01_2026-08-26.xlsx
+++ b/assets/xlsx/일별투자수익_2026-08-01_2026-08-26.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>연환산수익률</t>
+          <t>연환산 수익률</t>
         </is>
       </c>
     </row>
